--- a/任课与排课说明.xlsx
+++ b/任课与排课说明.xlsx
@@ -1,15 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\许办公文件\2026-2027上学期\课程\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="21600" windowHeight="10455"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +32,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1349" uniqueCount="237">
   <si>
-    <t>上午5节（8：00开始上课，每节38分钟），下午4节（2：20开始上，6、7、8节为40分钟1节，第9节4：50-5：30）</t>
+    <t>上午5节，下午4节</t>
   </si>
   <si>
     <t>姓名</t>
@@ -1376,15 +1371,12 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1923,28 +1915,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:J229"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9.025" defaultRowHeight="13.5"/>
   <cols>
-    <col min="4" max="4" width="50.9823008849558" style="1" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="10.8938053097345" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.2654867256637" customWidth="1"/>
-    <col min="8" max="8" width="31.5929203539823" customWidth="1"/>
-    <col min="9" max="9" width="23.7699115044248" customWidth="1"/>
+    <col min="4" max="4" width="50.9833333333333" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="10.8916666666667" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.2666666666667" customWidth="1"/>
+    <col min="8" max="8" width="31.5916666666667" customWidth="1"/>
+    <col min="9" max="9" width="23.7666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:10">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
@@ -1992,7 +1984,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
         <v>14</v>
@@ -2021,7 +2013,7 @@
         <v>2</v>
       </c>
       <c r="E4" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H4" t="s">
         <v>19</v>
@@ -2047,7 +2039,7 @@
         <v>21</v>
       </c>
       <c r="E5" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
         <v>14</v>
@@ -2076,7 +2068,7 @@
         <v>23</v>
       </c>
       <c r="E6" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
         <v>14</v>
@@ -2105,7 +2097,7 @@
         <v>25</v>
       </c>
       <c r="E7" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H7" t="s">
         <v>19</v>
@@ -2131,7 +2123,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H8" t="s">
         <v>19</v>
@@ -2157,7 +2149,7 @@
         <v>29</v>
       </c>
       <c r="E9" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H9" t="s">
         <v>19</v>
@@ -2183,7 +2175,7 @@
         <v>31</v>
       </c>
       <c r="E10" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
         <v>14</v>
@@ -2212,7 +2204,7 @@
         <v>33</v>
       </c>
       <c r="E11" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H11" t="s">
         <v>19</v>
@@ -2238,7 +2230,7 @@
         <v>35</v>
       </c>
       <c r="E12" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
         <v>14</v>
@@ -2267,7 +2259,7 @@
         <v>37</v>
       </c>
       <c r="E13" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H13" t="s">
         <v>19</v>
@@ -2293,7 +2285,7 @@
         <v>39</v>
       </c>
       <c r="E14" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H14" t="s">
         <v>19</v>
@@ -2319,7 +2311,7 @@
         <v>41</v>
       </c>
       <c r="E15" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H15" t="s">
         <v>19</v>
@@ -2345,7 +2337,7 @@
         <v>25</v>
       </c>
       <c r="E16" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F16" t="s">
         <v>14</v>
@@ -2374,7 +2366,7 @@
         <v>26</v>
       </c>
       <c r="E17" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F17" t="s">
         <v>44</v>
@@ -2403,7 +2395,7 @@
         <v>47</v>
       </c>
       <c r="E18" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F18" t="s">
         <v>14</v>
@@ -2432,7 +2424,7 @@
         <v>49</v>
       </c>
       <c r="E19" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F19" t="s">
         <v>14</v>
@@ -2461,7 +2453,7 @@
         <v>51</v>
       </c>
       <c r="E20" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F20" t="s">
         <v>14</v>
@@ -2518,7 +2510,6 @@
       <c r="E22" s="1">
         <v>5</v>
       </c>
-      <c r="F22"/>
       <c r="H22" t="s">
         <v>55</v>
       </c>
@@ -2594,7 +2585,6 @@
       <c r="E25" s="1">
         <v>5</v>
       </c>
-      <c r="F25"/>
       <c r="H25" t="s">
         <v>55</v>
       </c>
@@ -2618,7 +2608,6 @@
       <c r="E26" s="1">
         <v>5</v>
       </c>
-      <c r="F26"/>
       <c r="H26" t="s">
         <v>55</v>
       </c>
@@ -2668,7 +2657,6 @@
       <c r="E28" s="1">
         <v>5</v>
       </c>
-      <c r="F28"/>
       <c r="H28" t="s">
         <v>55</v>
       </c>
@@ -2796,7 +2784,6 @@
       <c r="E33" s="1">
         <v>5</v>
       </c>
-      <c r="F33"/>
       <c r="H33" t="s">
         <v>55</v>
       </c>
@@ -2820,7 +2807,6 @@
       <c r="E34" s="1">
         <v>5</v>
       </c>
-      <c r="F34"/>
       <c r="H34" t="s">
         <v>55</v>
       </c>
@@ -2844,7 +2830,6 @@
       <c r="E35" s="1">
         <v>5</v>
       </c>
-      <c r="F35"/>
       <c r="H35" t="s">
         <v>55</v>
       </c>
@@ -2920,7 +2905,6 @@
       <c r="E38" s="1">
         <v>5</v>
       </c>
-      <c r="F38"/>
       <c r="H38" t="s">
         <v>78</v>
       </c>
@@ -2944,7 +2928,6 @@
       <c r="E39" s="1">
         <v>5</v>
       </c>
-      <c r="F39"/>
       <c r="H39" t="s">
         <v>78</v>
       </c>
@@ -2968,7 +2951,6 @@
       <c r="E40" s="1">
         <v>5</v>
       </c>
-      <c r="F40"/>
       <c r="H40" t="s">
         <v>78</v>
       </c>
@@ -3018,7 +3000,6 @@
       <c r="E42" s="1">
         <v>5</v>
       </c>
-      <c r="F42"/>
       <c r="H42" t="s">
         <v>78</v>
       </c>
@@ -3068,7 +3049,6 @@
       <c r="E44" s="1">
         <v>5</v>
       </c>
-      <c r="F44"/>
       <c r="H44" t="s">
         <v>78</v>
       </c>
@@ -3144,7 +3124,6 @@
       <c r="E47" s="1">
         <v>5</v>
       </c>
-      <c r="F47"/>
       <c r="H47" t="s">
         <v>78</v>
       </c>
@@ -3194,7 +3173,6 @@
       <c r="E49" s="1">
         <v>5</v>
       </c>
-      <c r="F49"/>
       <c r="H49" t="s">
         <v>78</v>
       </c>
@@ -3270,7 +3248,6 @@
       <c r="E52" s="1">
         <v>5</v>
       </c>
-      <c r="F52"/>
       <c r="H52" t="s">
         <v>78</v>
       </c>
@@ -3294,7 +3271,6 @@
       <c r="E53" s="1">
         <v>5</v>
       </c>
-      <c r="F53"/>
       <c r="H53" t="s">
         <v>78</v>
       </c>
@@ -3318,7 +3294,6 @@
       <c r="E54" s="1">
         <v>5</v>
       </c>
-      <c r="F54"/>
       <c r="H54" t="s">
         <v>78</v>
       </c>
@@ -5280,7 +5255,7 @@
         <v>54</v>
       </c>
       <c r="E140" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G140" t="s">
         <v>228</v>
@@ -5300,7 +5275,7 @@
         <v>21</v>
       </c>
       <c r="E141" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G141" t="s">
         <v>228</v>
@@ -5320,7 +5295,7 @@
         <v>23</v>
       </c>
       <c r="E142" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G142" t="s">
         <v>228</v>
@@ -5340,7 +5315,7 @@
         <v>25</v>
       </c>
       <c r="E143" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F143" t="s">
         <v>14</v>
@@ -5366,7 +5341,7 @@
         <v>27</v>
       </c>
       <c r="E144" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G144" t="s">
         <v>228</v>
@@ -5386,7 +5361,7 @@
         <v>29</v>
       </c>
       <c r="E145" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F145" t="s">
         <v>14</v>
@@ -5412,7 +5387,7 @@
         <v>31</v>
       </c>
       <c r="E146" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G146" t="s">
         <v>228</v>
@@ -5432,7 +5407,7 @@
         <v>15</v>
       </c>
       <c r="E147" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F147" t="s">
         <v>87</v>
@@ -5458,7 +5433,7 @@
         <v>16</v>
       </c>
       <c r="E148" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F148" t="s">
         <v>90</v>
@@ -5484,7 +5459,7 @@
         <v>35</v>
       </c>
       <c r="E149" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G149" t="s">
         <v>228</v>
@@ -5504,7 +5479,7 @@
         <v>37</v>
       </c>
       <c r="E150" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F150" t="s">
         <v>14</v>
@@ -5530,7 +5505,7 @@
         <v>39</v>
       </c>
       <c r="E151" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G151" t="s">
         <v>228</v>
@@ -5550,7 +5525,7 @@
         <v>41</v>
       </c>
       <c r="E152" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F152" t="s">
         <v>14</v>
@@ -5576,7 +5551,7 @@
         <v>70</v>
       </c>
       <c r="E153" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F153" t="s">
         <v>14</v>
@@ -5602,7 +5577,7 @@
         <v>47</v>
       </c>
       <c r="E154" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G154" t="s">
         <v>228</v>
@@ -5622,7 +5597,7 @@
         <v>49</v>
       </c>
       <c r="E155" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G155" t="s">
         <v>228</v>
@@ -5642,7 +5617,7 @@
         <v>51</v>
       </c>
       <c r="E156" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G156" t="s">
         <v>228</v>
@@ -5662,7 +5637,7 @@
         <v>54</v>
       </c>
       <c r="E157" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F157" t="s">
         <v>14</v>
@@ -5688,7 +5663,7 @@
         <v>21</v>
       </c>
       <c r="E158" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G158" t="s">
         <v>230</v>
@@ -5708,7 +5683,7 @@
         <v>23</v>
       </c>
       <c r="E159" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F159" t="s">
         <v>14</v>
@@ -5734,7 +5709,7 @@
         <v>25</v>
       </c>
       <c r="E160" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F160" t="s">
         <v>14</v>
@@ -5760,7 +5735,7 @@
         <v>9</v>
       </c>
       <c r="E161" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G161" t="s">
         <v>230</v>
@@ -5780,7 +5755,7 @@
         <v>10</v>
       </c>
       <c r="E162" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G162" t="s">
         <v>230</v>
@@ -5800,7 +5775,7 @@
         <v>29</v>
       </c>
       <c r="E163" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F163" t="s">
         <v>14</v>
@@ -5826,7 +5801,7 @@
         <v>31</v>
       </c>
       <c r="E164" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G164" t="s">
         <v>230</v>
@@ -5846,7 +5821,7 @@
         <v>33</v>
       </c>
       <c r="E165" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F165" t="s">
         <v>14</v>
@@ -5872,7 +5847,7 @@
         <v>35</v>
       </c>
       <c r="E166" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F166" t="s">
         <v>14</v>
@@ -5898,7 +5873,7 @@
         <v>37</v>
       </c>
       <c r="E167" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F167" t="s">
         <v>14</v>
@@ -5924,7 +5899,7 @@
         <v>39</v>
       </c>
       <c r="E168" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F168" t="s">
         <v>14</v>
@@ -5950,7 +5925,7 @@
         <v>41</v>
       </c>
       <c r="E169" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G169" t="s">
         <v>230</v>
@@ -5970,7 +5945,7 @@
         <v>70</v>
       </c>
       <c r="E170" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G170" t="s">
         <v>230</v>
@@ -5990,7 +5965,7 @@
         <v>47</v>
       </c>
       <c r="E171" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G171" t="s">
         <v>230</v>
@@ -6010,7 +5985,7 @@
         <v>49</v>
       </c>
       <c r="E172" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F172" t="s">
         <v>14</v>
@@ -6036,7 +6011,7 @@
         <v>51</v>
       </c>
       <c r="E173" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F173" t="s">
         <v>74</v>
@@ -6062,7 +6037,7 @@
         <v>181</v>
       </c>
       <c r="E174" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G174" t="s">
         <v>232</v>
@@ -6082,7 +6057,7 @@
         <v>21</v>
       </c>
       <c r="E175" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F175" t="s">
         <v>74</v>
@@ -6108,7 +6083,7 @@
         <v>187</v>
       </c>
       <c r="E176" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G176" t="s">
         <v>232</v>
@@ -6128,7 +6103,7 @@
         <v>189</v>
       </c>
       <c r="E177" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G177" t="s">
         <v>232</v>
@@ -6148,7 +6123,7 @@
         <v>191</v>
       </c>
       <c r="E178" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G178" t="s">
         <v>232</v>
@@ -6168,7 +6143,7 @@
         <v>193</v>
       </c>
       <c r="E179" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G179" t="s">
         <v>232</v>
@@ -6188,7 +6163,7 @@
         <v>195</v>
       </c>
       <c r="E180" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G180" t="s">
         <v>232</v>
@@ -6208,7 +6183,7 @@
         <v>197</v>
       </c>
       <c r="E181" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G181" t="s">
         <v>232</v>
@@ -6228,7 +6203,7 @@
         <v>199</v>
       </c>
       <c r="E182" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G182" t="s">
         <v>232</v>
@@ -6248,7 +6223,7 @@
         <v>26</v>
       </c>
       <c r="E183" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F183" t="s">
         <v>201</v>
@@ -6274,7 +6249,7 @@
         <v>203</v>
       </c>
       <c r="E184" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G184" t="s">
         <v>232</v>
@@ -6294,7 +6269,7 @@
         <v>205</v>
       </c>
       <c r="E185" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G185" t="s">
         <v>232</v>
